--- a/project/outputs_xlsx_solution/prog-loop.4-wide-NB-1.xlsx
+++ b/project/outputs_xlsx_solution/prog-loop.4-wide-NB-1.xlsx
@@ -746,6 +746,21 @@
         <v>21</v>
       </c>
       <c r="N6" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" t="s">
+        <v>21</v>
+      </c>
+      <c r="P6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>21</v>
+      </c>
+      <c r="R6" t="s">
+        <v>21</v>
+      </c>
+      <c r="S6" t="s">
         <v>22</v>
       </c>
     </row>
@@ -774,7 +789,7 @@
       <c r="L7" t="s">
         <v>20</v>
       </c>
-      <c r="N7" t="s">
+      <c r="S7" t="s">
         <v>22</v>
       </c>
     </row>
@@ -797,28 +812,16 @@
       <c r="G8" t="s">
         <v>16</v>
       </c>
-      <c r="N8" t="s">
-        <v>14</v>
-      </c>
-      <c r="O8" t="s">
-        <v>14</v>
-      </c>
-      <c r="P8" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>21</v>
-      </c>
-      <c r="R8" t="s">
-        <v>21</v>
-      </c>
       <c r="S8" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="T8" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="U8" t="s">
+        <v>14</v>
+      </c>
+      <c r="V8" t="s">
         <v>22</v>
       </c>
     </row>
@@ -841,13 +844,13 @@
       <c r="G9" t="s">
         <v>16</v>
       </c>
-      <c r="U9" t="s">
-        <v>14</v>
-      </c>
       <c r="V9" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="W9" t="s">
+        <v>21</v>
+      </c>
+      <c r="X9" t="s">
         <v>22</v>
       </c>
     </row>
@@ -876,7 +879,7 @@
       <c r="J10" t="s">
         <v>20</v>
       </c>
-      <c r="W10" t="s">
+      <c r="X10" t="s">
         <v>22</v>
       </c>
     </row>
@@ -908,7 +911,7 @@
       <c r="M11" t="s">
         <v>20</v>
       </c>
-      <c r="W11" t="s">
+      <c r="X11" t="s">
         <v>22</v>
       </c>
     </row>
@@ -937,7 +940,7 @@
       <c r="K12" t="s">
         <v>20</v>
       </c>
-      <c r="W12" t="s">
+      <c r="X12" t="s">
         <v>22</v>
       </c>
     </row>
@@ -958,15 +961,12 @@
         <v>9</v>
       </c>
       <c r="M13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N13" t="s">
-        <v>14</v>
-      </c>
-      <c r="O13" t="s">
-        <v>20</v>
-      </c>
-      <c r="X13" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y13" t="s">
         <v>22</v>
       </c>
     </row>
@@ -989,31 +989,37 @@
       <c r="M14" t="s">
         <v>16</v>
       </c>
+      <c r="N14" t="s">
+        <v>15</v>
+      </c>
       <c r="O14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="Q14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S14" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="T14" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="U14" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="V14" t="s">
-        <v>20</v>
-      </c>
-      <c r="X14" t="s">
+        <v>14</v>
+      </c>
+      <c r="W14" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y14" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1034,18 +1040,15 @@
         <v>9</v>
       </c>
       <c r="M15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="N15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="O15" t="s">
-        <v>14</v>
-      </c>
-      <c r="P15" t="s">
-        <v>20</v>
-      </c>
-      <c r="X15" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y15" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1068,9 +1071,6 @@
       <c r="M16" t="s">
         <v>16</v>
       </c>
-      <c r="V16" t="s">
-        <v>14</v>
-      </c>
       <c r="W16" t="s">
         <v>14</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>14</v>
       </c>
       <c r="Y16" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="Z16" t="s">
         <v>21</v>
@@ -1133,15 +1133,12 @@
         <v>9</v>
       </c>
       <c r="N18" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="O18" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="P18" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q18" t="s">
         <v>20</v>
       </c>
       <c r="AC18" t="s">
@@ -1165,21 +1162,18 @@
         <v>9</v>
       </c>
       <c r="N19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="O19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P19" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="Q19" t="s">
         <v>21</v>
       </c>
       <c r="R19" t="s">
-        <v>21</v>
-      </c>
-      <c r="S19" t="s">
         <v>20</v>
       </c>
       <c r="AC19" t="s">
@@ -1205,10 +1199,10 @@
       <c r="N20" t="s">
         <v>16</v>
       </c>
+      <c r="P20" t="s">
+        <v>14</v>
+      </c>
       <c r="Q20" t="s">
-        <v>14</v>
-      </c>
-      <c r="R20" t="s">
         <v>20</v>
       </c>
       <c r="AC20" t="s">
@@ -1234,10 +1228,10 @@
       <c r="O21" t="s">
         <v>16</v>
       </c>
+      <c r="P21" t="s">
+        <v>14</v>
+      </c>
       <c r="Q21" t="s">
-        <v>14</v>
-      </c>
-      <c r="R21" t="s">
         <v>20</v>
       </c>
       <c r="AD21" t="s">
@@ -1261,10 +1255,16 @@
         <v>9</v>
       </c>
       <c r="O22" t="s">
-        <v>16</v>
+        <v>23</v>
+      </c>
+      <c r="P22" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>23</v>
       </c>
       <c r="R22" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="S22" t="s">
         <v>15</v>
@@ -1276,7 +1276,7 @@
         <v>15</v>
       </c>
       <c r="V22" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W22" t="s">
         <v>14</v>
@@ -1288,7 +1288,7 @@
         <v>14</v>
       </c>
       <c r="Z22" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AA22" t="s">
         <v>21</v>
@@ -1315,12 +1315,6 @@
       </c>
       <c r="N23" t="s">
         <v>9</v>
-      </c>
-      <c r="O23" t="s">
-        <v>23</v>
-      </c>
-      <c r="P23" t="s">
-        <v>16</v>
       </c>
       <c r="S23" t="s">
         <v>14</v>
@@ -1348,15 +1342,6 @@
       <c r="N24" t="s">
         <v>9</v>
       </c>
-      <c r="P24" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>24</v>
-      </c>
-      <c r="R24" t="s">
-        <v>24</v>
-      </c>
       <c r="S24" t="s">
         <v>24</v>
       </c>
@@ -1364,6 +1349,9 @@
         <v>24</v>
       </c>
       <c r="U24" t="s">
+        <v>24</v>
+      </c>
+      <c r="V24" t="s">
         <v>16</v>
       </c>
       <c r="AB24" t="s">
@@ -1395,13 +1383,13 @@
       <c r="O25" t="s">
         <v>9</v>
       </c>
-      <c r="U25" t="s">
-        <v>23</v>
-      </c>
       <c r="V25" t="s">
         <v>23</v>
       </c>
       <c r="W25" t="s">
+        <v>23</v>
+      </c>
+      <c r="X25" t="s">
         <v>16</v>
       </c>
       <c r="AE25" t="s">
@@ -1427,9 +1415,6 @@
       <c r="O26" t="s">
         <v>9</v>
       </c>
-      <c r="W26" t="s">
-        <v>16</v>
-      </c>
       <c r="X26" t="s">
         <v>14</v>
       </c>
@@ -1456,9 +1441,6 @@
       <c r="O27" t="s">
         <v>9</v>
       </c>
-      <c r="W27" t="s">
-        <v>16</v>
-      </c>
       <c r="X27" t="s">
         <v>15</v>
       </c>
@@ -1488,7 +1470,7 @@
       <c r="O28" t="s">
         <v>9</v>
       </c>
-      <c r="W28" t="s">
+      <c r="X28" t="s">
         <v>16</v>
       </c>
       <c r="Y28" t="s">
